--- a/LangMod/EN/Quests.xlsx
+++ b/LangMod/EN/Quests.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="336">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1888,10 +1888,6 @@
       </rPr>
       <t xml:space="preserve">_fighter_dungeon_attack</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">The guild is running a “Let’s Clear a Nefia” campaign. It’s simple — just clear one Nefia anywhere you like. Why not join?
-We’ve received a request from the settlers of Misiria. They’d like Nefias suppressed to increase the number of safe settlement candidates, even if only a little. Clear any Nefia you can find; once you defeat the boss the lesser enemies will scatter on their own. </t>
   </si>
   <si>
     <r>
@@ -3523,37 +3519,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -5108,7 +5104,7 @@
         <v>174</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="9"/>
@@ -5117,16 +5113,16 @@
     </row>
     <row r="38" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="D38" s="14" t="s">
         <v>226</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>227</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="12"/>
@@ -5146,10 +5142,10 @@
         <v>53</v>
       </c>
       <c r="L38" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="M38" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="9"/>
@@ -5158,16 +5154,16 @@
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="C39" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -5175,19 +5171,19 @@
         <v>173</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="L39" s="8" t="s">
+      <c r="M39" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>237</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="9"/>
@@ -5196,16 +5192,16 @@
     </row>
     <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="D40" s="15" t="s">
         <v>240</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>241</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -5213,7 +5209,7 @@
         <v>26</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>37</v>
@@ -5225,10 +5221,10 @@
         <v>28</v>
       </c>
       <c r="L40" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M40" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="9"/>
@@ -5237,16 +5233,16 @@
     </row>
     <row r="41" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="C41" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -5254,7 +5250,7 @@
         <v>26</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>53</v>
@@ -5266,10 +5262,10 @@
         <v>37</v>
       </c>
       <c r="L41" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="M41" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="N41" s="3"/>
       <c r="P41" s="9"/>
@@ -5277,16 +5273,16 @@
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="D42" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -5294,7 +5290,7 @@
         <v>26</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>199</v>
@@ -5306,10 +5302,10 @@
         <v>38</v>
       </c>
       <c r="L42" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="M42" s="17" t="s">
         <v>255</v>
-      </c>
-      <c r="M42" s="17" t="s">
-        <v>256</v>
       </c>
       <c r="N42" s="7"/>
       <c r="O42" s="4"/>
@@ -5318,16 +5314,16 @@
     </row>
     <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="D43" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -5335,7 +5331,7 @@
         <v>26</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>62</v>
@@ -5347,10 +5343,10 @@
         <v>38</v>
       </c>
       <c r="L43" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="M43" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="9"/>
@@ -5359,16 +5355,16 @@
     </row>
     <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="C44" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="D44" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -5376,7 +5372,7 @@
         <v>26</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>199</v>
@@ -5388,10 +5384,10 @@
         <v>37</v>
       </c>
       <c r="L44" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="M44" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="4"/>
@@ -5400,16 +5396,16 @@
     </row>
     <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="D45" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="E45" s="9"/>
       <c r="F45" s="12"/>
@@ -5417,7 +5413,7 @@
         <v>26</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>76</v>
@@ -5429,10 +5425,10 @@
         <v>148</v>
       </c>
       <c r="L45" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="M45" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="9"/>
@@ -5441,16 +5437,16 @@
     </row>
     <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -5458,7 +5454,7 @@
         <v>152</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>199</v>
@@ -5470,10 +5466,10 @@
         <v>38</v>
       </c>
       <c r="L46" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="M46" s="17" t="s">
         <v>255</v>
-      </c>
-      <c r="M46" s="17" t="s">
-        <v>256</v>
       </c>
       <c r="N46" s="7"/>
       <c r="O46" s="4"/>
@@ -5482,16 +5478,16 @@
     </row>
     <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="D47" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -5499,7 +5495,7 @@
         <v>152</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>62</v>
@@ -5511,10 +5507,10 @@
         <v>38</v>
       </c>
       <c r="L47" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="M47" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="9"/>
@@ -5523,16 +5519,16 @@
     </row>
     <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="D48" s="15" t="s">
         <v>240</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>241</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -5540,7 +5536,7 @@
         <v>152</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>37</v>
@@ -5552,10 +5548,10 @@
         <v>28</v>
       </c>
       <c r="L48" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M48" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="9"/>
@@ -5564,16 +5560,16 @@
     </row>
     <row r="49" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="C49" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="D49" s="12" t="s">
         <v>280</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>281</v>
       </c>
       <c r="E49" s="9"/>
       <c r="F49" s="12"/>
@@ -5581,7 +5577,7 @@
         <v>152</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>199</v>
@@ -5593,10 +5589,10 @@
         <v>62</v>
       </c>
       <c r="L49" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="M49" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="9"/>
@@ -5605,16 +5601,16 @@
     </row>
     <row r="50" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B50" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="C50" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="D50" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>287</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="12"/>
@@ -5622,7 +5618,7 @@
         <v>26</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>121</v>
@@ -5634,10 +5630,10 @@
         <v>38</v>
       </c>
       <c r="L50" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="M50" s="17" t="s">
         <v>289</v>
-      </c>
-      <c r="M50" s="17" t="s">
-        <v>290</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="9"/>
@@ -5646,16 +5642,16 @@
     </row>
     <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="D51" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
@@ -5663,7 +5659,7 @@
         <v>26</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>62</v>
@@ -5675,10 +5671,10 @@
         <v>38</v>
       </c>
       <c r="L51" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="M51" s="12" t="s">
         <v>296</v>
-      </c>
-      <c r="M51" s="12" t="s">
-        <v>297</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="9"/>
@@ -5687,16 +5683,16 @@
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="D52" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="E52" s="9"/>
       <c r="F52" s="12"/>
@@ -5704,7 +5700,7 @@
         <v>26</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>135</v>
@@ -5716,10 +5712,10 @@
         <v>38</v>
       </c>
       <c r="L52" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="M52" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="9"/>
@@ -5728,16 +5724,16 @@
     </row>
     <row r="53" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="D53" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="E53" s="9"/>
       <c r="F53" s="12"/>
@@ -5745,7 +5741,7 @@
         <v>26</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>121</v>
@@ -5757,10 +5753,10 @@
         <v>38</v>
       </c>
       <c r="L53" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="M53" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="9"/>
@@ -5769,16 +5765,16 @@
     </row>
     <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="D54" s="15" t="s">
         <v>312</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>313</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="12"/>
@@ -5786,7 +5782,7 @@
         <v>26</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>37</v>
@@ -5798,10 +5794,10 @@
         <v>28</v>
       </c>
       <c r="L54" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="M54" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="M54" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="9"/>
@@ -5810,16 +5806,16 @@
     </row>
     <row r="55" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="C55" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="D55" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="E55" s="9"/>
       <c r="F55" s="3"/>
@@ -5827,7 +5823,7 @@
         <v>26</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>76</v>
@@ -5839,10 +5835,10 @@
         <v>148</v>
       </c>
       <c r="L55" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="M55" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="9"/>
@@ -5851,16 +5847,16 @@
     </row>
     <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="D56" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
@@ -5868,7 +5864,7 @@
         <v>152</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>62</v>
@@ -5880,10 +5876,10 @@
         <v>38</v>
       </c>
       <c r="L56" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="M56" s="12" t="s">
         <v>296</v>
-      </c>
-      <c r="M56" s="12" t="s">
-        <v>297</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="9"/>
@@ -5892,16 +5888,16 @@
     </row>
     <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="D57" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="E57" s="9"/>
       <c r="F57" s="12"/>
@@ -5909,7 +5905,7 @@
         <v>152</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>135</v>
@@ -5921,10 +5917,10 @@
         <v>38</v>
       </c>
       <c r="L57" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="M57" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="9"/>
@@ -5933,16 +5929,16 @@
     </row>
     <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="C58" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="D58" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -5950,7 +5946,7 @@
         <v>152</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>53</v>
@@ -5962,10 +5958,10 @@
         <v>53</v>
       </c>
       <c r="L58" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="M58" s="6" t="s">
         <v>329</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="9"/>
@@ -5974,16 +5970,16 @@
     </row>
     <row r="59" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="D59" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="9"/>
@@ -5991,7 +5987,7 @@
         <v>152</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>53</v>
@@ -6003,10 +5999,10 @@
         <v>53</v>
       </c>
       <c r="L59" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="M59" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="M59" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="9"/>

--- a/LangMod/EN/Quests.xlsx
+++ b/LangMod/EN/Quests.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Quest" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Quest!$A$3:$Q$59</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Quest!$A$3:$Q$60</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="343">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -346,6 +346,112 @@
 While I looked away for just a moment, wild animals ate my crops! They might not mean any harm, but I can't let them treat my field as their feeding ground. Please teach those pests a lesson. </t>
   </si>
   <si>
+    <t xml:space="preserve">byakko_mod_common_road_war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">求む！勇士！
+防衛線を死守せよ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guadians 6 or more, Siege
+Hold ranks!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestRoadDefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">斥侯から、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2の大群が街に向かっているとの情報が入った{よ}。とにかく</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">数が多いらしくて{ね}、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">戦力補強のため、有志の冒険者を募っている{のだ}。謝礼として#1が貰えるの{だが}、興味はない{か}？
+まずいことになった{よ}。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">#2の大群と戦闘中だった駐屯部隊が、かなり押されてきてしまっている{のだ}。このままでは進入されるのも時間の問題{だろう}。誰でもいい{よ}、どうか援護に入ってくれない{か}？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">We've received word from our outpost that a horde of #2 is heading toward the town. Apparently, their numbers are overwhelming, so we're looking for volunteer adventurers to reinforce our forces. There's a reward of #1 in it for you—interested? 
+Things have taken a turn for the worse. The garrison forces engaged with the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">horde of #2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> are being pushed back heavily. If this continues, it will only be a matter of time before the enemy breaches our defenses. It doesn't matter who comes—please, lend us your aid. </t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">byakko_mod_common_urban_intrusion</t>
   </si>
   <si>
@@ -784,9 +890,6 @@
   </si>
   <si>
     <t xml:space="preserve">merchant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
   </si>
   <si>
     <r>
@@ -3316,6 +3419,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="1"/>
@@ -3325,13 +3435,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
@@ -3405,7 +3508,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3451,6 +3554,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3458,7 +3565,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3622,7 +3729,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.06"/>
@@ -3972,8 +4079,8 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -3982,49 +4089,49 @@
       <c r="C9" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>29</v>
+        <v>69</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="M9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>71</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -4035,7 +4142,7 @@
         <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>29</v>
@@ -4054,17 +4161,17 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="3" t="s">
         <v>83</v>
       </c>
       <c r="E11" s="3"/>
@@ -4073,40 +4180,40 @@
         <v>26</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M11" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N11" s="4"/>
+      <c r="M11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="B12" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="C12" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="3" t="s">
         <v>90</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -4114,134 +4221,134 @@
         <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>29</v>
+      <c r="J12" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>37</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="M12" s="11" t="s">
         <v>93</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="D13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>98</v>
+      <c r="H13" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="12" t="s">
+      <c r="M13" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="N13" s="3"/>
+      <c r="N13" s="4"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>107</v>
+      <c r="L14" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="C15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>99</v>
+      <c r="H15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L15" s="4" t="s">
@@ -4251,6 +4358,9 @@
         <v>116</v>
       </c>
       <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -4271,16 +4381,16 @@
         <v>26</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>122</v>
@@ -4294,29 +4404,31 @@
       <c r="A17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>127</v>
       </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>129</v>
@@ -4326,7 +4438,7 @@
       </c>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>131</v>
       </c>
@@ -4343,16 +4455,16 @@
         <v>26</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>135</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>136</v>
@@ -4362,7 +4474,7 @@
       </c>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>138</v>
       </c>
@@ -4379,54 +4491,54 @@
         <v>26</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L20" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>149</v>
       </c>
       <c r="M20" s="4" t="s">
@@ -4434,47 +4546,45 @@
       </c>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>111</v>
+      <c r="B21" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+        <v>154</v>
+      </c>
       <c r="G21" s="1" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>99</v>
+        <v>121</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>115</v>
+        <v>45</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="N21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>118</v>
@@ -4488,19 +4598,19 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>122</v>
@@ -4512,183 +4622,180 @@
     </row>
     <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>140</v>
+        <v>160</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>135</v>
+        <v>121</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>62</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="I25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="L25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C25" s="4" t="s">
+    <row r="26" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="H26" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="K25" s="3" t="s">
+      <c r="J26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="N25" s="3"/>
+      <c r="L26" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="N26" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>174</v>
@@ -4697,9 +4804,9 @@
         <v>175</v>
       </c>
       <c r="N27" s="3"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
@@ -4711,7 +4818,7 @@
       <c r="C28" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="9" t="s">
         <v>179</v>
       </c>
       <c r="E28" s="3"/>
@@ -4720,98 +4827,98 @@
         <v>26</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>180</v>
+        <v>62</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
     </row>
-    <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>182</v>
+    <row r="29" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="12"/>
+        <v>186</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
       <c r="G29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>76</v>
+        <v>108</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
     </row>
-    <row r="30" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>188</v>
+    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E30" s="9"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="13"/>
       <c r="G30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>193</v>
@@ -4825,7 +4932,7 @@
       <c r="Q30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="14" t="s">
         <v>195</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -4837,22 +4944,22 @@
       <c r="D31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="12"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>200</v>
@@ -4865,8 +4972,8 @@
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
     </row>
-    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
+    <row r="32" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
         <v>202</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -4879,27 +4986,27 @@
         <v>205</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="13"/>
       <c r="G32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="9"/>
@@ -4907,163 +5014,163 @@
       <c r="Q32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>208</v>
+      <c r="A33" s="14" t="s">
+        <v>209</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E33" s="3"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="13"/>
       <c r="G33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
     </row>
-    <row r="34" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>214</v>
+    <row r="34" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="F34" s="13"/>
       <c r="G34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>45</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>218</v>
+        <v>38</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
     </row>
-    <row r="35" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>220</v>
+    <row r="35" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="3"/>
       <c r="G35" s="1" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>206</v>
+        <v>155</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
     </row>
-    <row r="36" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>221</v>
+    <row r="36" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="13"/>
       <c r="G36" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="9"/>
@@ -5071,159 +5178,159 @@
       <c r="Q36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>222</v>
+      <c r="A37" s="14" t="s">
+        <v>228</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>172</v>
+        <v>204</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>37</v>
+        <v>206</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L37" s="8" t="s">
-        <v>174</v>
+      <c r="L37" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
     </row>
-    <row r="38" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>223</v>
+    <row r="38" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>229</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>226</v>
+        <v>177</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>179</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="3"/>
       <c r="G38" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>228</v>
+        <v>181</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
     </row>
-    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>229</v>
+    <row r="39" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>230</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D39" s="3" t="s">
         <v>231</v>
       </c>
+      <c r="C39" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>233</v>
+      </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="H39" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>232</v>
+        <v>53</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="K39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="L39" s="8" t="s">
+      <c r="M39" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>236</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
     </row>
-    <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>240</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="G40" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="H40" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="M40" s="4" t="s">
+      <c r="M40" s="8" t="s">
         <v>243</v>
       </c>
       <c r="N40" s="3"/>
@@ -5231,7 +5338,7 @@
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
     </row>
-    <row r="41" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>244</v>
       </c>
@@ -5241,7 +5348,7 @@
       <c r="C41" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="16" t="s">
         <v>247</v>
       </c>
       <c r="E41" s="3"/>
@@ -5250,39 +5357,40 @@
         <v>26</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N41" s="3"/>
+      <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
     </row>
-    <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>250</v>
+    <row r="42" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -5290,40 +5398,39 @@
         <v>26</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="M42" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="N42" s="7"/>
-      <c r="O42" s="4"/>
+      <c r="M42" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="N42" s="3"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
     </row>
-    <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
-        <v>256</v>
+    <row r="43" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -5331,40 +5438,40 @@
         <v>26</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="M43" s="4" t="s">
+      <c r="L43" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="N43" s="3"/>
-      <c r="O43" s="9"/>
+      <c r="M43" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="N43" s="7"/>
+      <c r="O43" s="4"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
     </row>
-    <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
-        <v>262</v>
+    <row r="44" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -5372,267 +5479,267 @@
         <v>26</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>266</v>
+        <v>38</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N44" s="3"/>
-      <c r="O44" s="4"/>
+      <c r="O44" s="9"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
     </row>
-    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
-        <v>268</v>
+    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="12"/>
+        <v>272</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
       <c r="G45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L45" s="13" t="s">
-        <v>272</v>
+        <v>37</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>273</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N45" s="3"/>
-      <c r="O45" s="9"/>
+      <c r="O45" s="4"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
     </row>
-    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>274</v>
+    <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>275</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+        <v>278</v>
+      </c>
+      <c r="E46" s="9"/>
+      <c r="F46" s="13"/>
       <c r="G46" s="1" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L46" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="M46" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="N46" s="7"/>
-      <c r="O46" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="L46" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="N46" s="3"/>
+      <c r="O46" s="9"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
     </row>
-    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="s">
-        <v>275</v>
+    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>281</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L47" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="M47" s="4" t="s">
+      <c r="L47" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="N47" s="3"/>
-      <c r="O47" s="9"/>
+      <c r="M47" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="N47" s="7"/>
+      <c r="O47" s="4"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>276</v>
+      <c r="A48" s="8" t="s">
+        <v>282</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>240</v>
+        <v>265</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="9"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
     </row>
-    <row r="49" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
-        <v>277</v>
+    <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="12"/>
+        <v>246</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
       <c r="G49" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L49" s="8" t="s">
-        <v>281</v>
+        <v>70</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>249</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="9"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
     </row>
-    <row r="50" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B50" s="12" t="s">
+    <row r="50" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="B50" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="12"/>
+      <c r="D50" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="E50" s="9"/>
+      <c r="F50" s="13"/>
       <c r="G50" s="1" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L50" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L50" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="M50" s="17" t="s">
+      <c r="M50" s="4" t="s">
         <v>289</v>
       </c>
       <c r="N50" s="3"/>
@@ -5640,40 +5747,40 @@
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
     </row>
-    <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+    <row r="51" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="13"/>
       <c r="G51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H51" s="15" t="s">
+      <c r="H51" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K51" s="1" t="s">
+      <c r="I51" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K51" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L51" s="4" t="s">
+      <c r="L51" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="M51" s="12" t="s">
+      <c r="M51" s="18" t="s">
         <v>296</v>
       </c>
       <c r="N51" s="3"/>
@@ -5681,82 +5788,82 @@
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
     </row>
-    <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="1" t="s">
         <v>300</v>
       </c>
       <c r="E52" s="9"/>
-      <c r="F52" s="12"/>
+      <c r="F52" s="9"/>
       <c r="G52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>287</v>
+      <c r="H52" s="16" t="s">
+        <v>301</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="M52" s="4" t="s">
         <v>302</v>
+      </c>
+      <c r="M52" s="13" t="s">
+        <v>303</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
     </row>
-    <row r="53" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="D53" s="1" t="s">
         <v>306</v>
       </c>
+      <c r="D53" s="9" t="s">
+        <v>307</v>
+      </c>
       <c r="E53" s="9"/>
-      <c r="F53" s="12"/>
+      <c r="F53" s="13"/>
       <c r="G53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="9"/>
@@ -5765,229 +5872,229 @@
     </row>
     <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D54" s="15" t="s">
         <v>312</v>
       </c>
+      <c r="D54" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="E54" s="9"/>
-      <c r="F54" s="12"/>
+      <c r="F54" s="13"/>
       <c r="G54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>313</v>
+        <v>45</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
     </row>
-    <row r="55" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="D55" s="3" t="s">
         <v>318</v>
       </c>
+      <c r="D55" s="16" t="s">
+        <v>319</v>
+      </c>
       <c r="E55" s="9"/>
-      <c r="F55" s="3"/>
+      <c r="F55" s="13"/>
       <c r="G55" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>319</v>
+        <v>70</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="9"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="9"/>
     </row>
-    <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>293</v>
+        <v>322</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
+      <c r="F56" s="3"/>
       <c r="G56" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H56" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>294</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="M56" s="12" t="s">
-        <v>296</v>
+        <v>326</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>327</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="9"/>
     </row>
-    <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B57" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="1" t="s">
         <v>300</v>
       </c>
       <c r="E57" s="9"/>
-      <c r="F57" s="12"/>
+      <c r="F57" s="9"/>
       <c r="G57" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>287</v>
+        <v>159</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>301</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="M57" s="4" t="s">
         <v>302</v>
+      </c>
+      <c r="M57" s="13" t="s">
+        <v>303</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="9"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="9"/>
     </row>
-    <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="s">
-        <v>323</v>
+    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
+        <v>305</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="E58" s="9"/>
+      <c r="F58" s="13"/>
       <c r="G58" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L58" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>329</v>
+        <v>38</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>309</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
     </row>
-    <row r="59" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="4" t="s">
         <v>332</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>333</v>
       </c>
       <c r="E59" s="3"/>
-      <c r="F59" s="9"/>
+      <c r="F59" s="3"/>
       <c r="G59" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>53</v>
@@ -5998,19 +6105,60 @@
       <c r="K59" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L59" s="4" t="s">
-        <v>334</v>
+      <c r="L59" s="14" t="s">
+        <v>335</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
     </row>
+    <row r="60" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="N60" s="3"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:Q59"/>
+  <autoFilter ref="A3:Q60"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/LangMod/EN/Quests.xlsx
+++ b/LangMod/EN/Quests.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Quest" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Quest!$A$3:$Q$60</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Quest!$A$3:$Q$61</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="348">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -706,6 +706,56 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">byakko_mod_common_music_filth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異文化交流
+文化の伝道師</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-Cultural Exchange
+Cultural Ambassador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestMusicFilth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文化も言葉も違う魔物達でも、音楽なら分かり合える気がする{のだ}。魔物達のねぐらで一曲演奏して、友好を伝えてきてくれない{か}？もしダメそうだったら、ボコボコにして構わない{よ}。
+{I}は思う{のだ}。魔物達を魔物達たらしめるのは、その野蛮さにあると{な}。なら、音楽という文化を伝えれば、いずれは共栄も夢じゃないのかもしれない{ね}？というわけで、魔物達に音楽の素晴らしさを伝えてきて{くれ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Even monsters with different cultures and languages might be able to understand each other through music. Could you play a song in their lair and try to make friends with them? If that doesn't work out, feel free to beat them to a pulp.
+I believe what makes monsters monsters is their savagery. If we can introduce them to the culture of music, perhaps one day we can even live together in harmony, don't you think? So, go out there and show those monsters the beauty of music.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_common_music_noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">命懸けの即興
+死よりの招待状</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impromptu ad Mortem
+Invitation from Death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestMusicNoble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この前、恐ろしい魔物に襲われた際に命乞いをしたの{だが}、何を口走ってしまったか彼らのパーティーの余興を用意することになった{のだ}！芸なんて{I}には無理{だよ}、代わりになんとかして{くれ}！
+以前うっかり怒らせた魔物から、{I}にパーティーへの招待状が届いた{よ}。余興役として{ね}。{だが}、こんなパーティーに出てたら命がいくつあっても足りない{よ}！報酬は弾むから、代理で出席して{くれ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The other day, I begged for my life when I was attacked by some terrifying monsters, but somehow, I ended up agreeing to provide entertainment for their party! I'm no performer, so there's no way I can pull this off. Please, you've got to do something in my place!
+I received an invitation to a party from some monsters I accidentally angered a while back. As the entertainment, of all things! But I'd never survive a party like that! I'll pay you handsomely, so please attend in my place.</t>
+  </si>
+  <si>
     <t xml:space="preserve">byakko_mod_guild_merchant_deliver</t>
   </si>
   <si>
@@ -1031,9 +1081,6 @@
     <t xml:space="preserve">QuestMGShipping</t>
   </si>
   <si>
-    <t xml:space="preserve">700</t>
-  </si>
-  <si>
     <t xml:space="preserve">{YOU}は開拓地を運営していると聞いたことがある{よ}。実は{I}も興味が{ある}。どうやって資金調達をしているのか気になる{のだ}、実際に#2オレンほど出荷するところを見せて{くれ}。心配{ない}、見えない所からこっそり観察させてもらう{よ}。
 生産者のことを良く知っておくことも商人として大切{だな}。{YOU}も開拓地から出荷をするの{か}？なら、#2オレンほど出荷してみてくれ。</t>
   </si>
@@ -1339,7 +1386,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">I've got an important meeting with the [qClient] coming up, and I'm worried they'll look down on me if my place is filled with nothing but ordinary furniture. So, I'd like to get something more luxurious. A high-end bed should do nicely.
+    <t xml:space="preserve">I've got an important meeting with the [qClient] coming up, and I'm worried they'll look down on me if my place is filled with nothing but ordinary furniture. So, I'd like to get something more luxurious. A #1 of #2 and #3 should do nicely.
 I'm thinking of giving a #1 to the [qClient] as a gesture of goodwill, but the problem is they're famous for being incredibly picky. An ordinary one probably won't satisfy them. Could you make a #1 of #2 and #3 worthy of their standards and bring it to me?</t>
   </si>
   <si>
@@ -2042,81 +2089,6 @@
   <si>
     <t xml:space="preserve">Have you ever heard of werewolves? They disguise themselves as humans, blend in with ordinary people, and commit murders without anyone noticing. I've actually been hired to hunt one down. I've received information that there's one in this town, but I still haven't managed to find it. I'll pay you #1 if you help me take it down. 
 Have you heard about the sudden increase in murders around this town? The guild has been asked to assist with the investigation, and we're currently planning to set up a stakeout. Once the case is solved, there'll be #1 reward. Would you be willing to help us? </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">byakko_mod_guild</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">_liaison</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">_fighter_subdue_cave</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">モンスター退治の専門家
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">モンスター退治の専門家</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">QuestFGSubdueCave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1919810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">364364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没クエスト。
-没クエスト。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut Quest. No need to translate or filter.
-Cut Quest. No need to translate or filter.</t>
   </si>
   <si>
     <t xml:space="preserve">byakko_mod_guild_mage_dungeon_retrieve</t>
@@ -3729,7 +3701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.06"/>
@@ -4285,150 +4257,153 @@
       <c r="Q13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="10" t="s">
         <v>107</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="13" t="s">
+      <c r="M14" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="N14" s="3"/>
+      <c r="N14" s="4"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="15" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" s="4" t="s">
+      <c r="M15" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N15" s="3"/>
+      <c r="N15" s="4"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
       <c r="G16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L16" s="4" t="s">
-        <v>122</v>
+      <c r="L16" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="D17" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>62</v>
+        <v>122</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>129</v>
@@ -4437,33 +4412,38 @@
         <v>130</v>
       </c>
       <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>134</v>
       </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="L18" s="4" t="s">
@@ -4474,33 +4454,35 @@
       </c>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>140</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>141</v>
       </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
       <c r="G19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>142</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>143</v>
@@ -4527,54 +4509,54 @@
         <v>26</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L21" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>156</v>
       </c>
       <c r="M21" s="4" t="s">
@@ -4586,222 +4568,219 @@
       <c r="A22" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>119</v>
+      <c r="B22" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+        <v>161</v>
+      </c>
       <c r="G22" s="1" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>107</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>38</v>
+        <v>122</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>126</v>
+        <v>164</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+        <v>167</v>
+      </c>
       <c r="G23" s="1" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>129</v>
+        <v>45</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="N23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>147</v>
+        <v>171</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>148</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="J24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>169</v>
+      <c r="M26" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="H27" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>174</v>
+        <v>38</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -4809,89 +4788,82 @@
       <c r="Q27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="A28" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="G28" s="1" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L28" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="M28" s="8" t="s">
         <v>182</v>
       </c>
       <c r="N28" s="3"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
     </row>
-    <row r="29" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+    <row r="29" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
       <c r="G29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="8" t="s">
         <v>187</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>188</v>
       </c>
       <c r="N29" s="3"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
+    <row r="30" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>189</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -4900,31 +4872,31 @@
       <c r="C30" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="13"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
       <c r="G30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>193</v>
+        <v>122</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="9"/>
@@ -4932,34 +4904,34 @@
       <c r="Q30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
-        <v>195</v>
+      <c r="A31" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="13"/>
+        <v>199</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
       <c r="G31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>199</v>
+        <v>122</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>200</v>
@@ -4972,7 +4944,7 @@
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
     </row>
-    <row r="32" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
         <v>202</v>
       </c>
@@ -4985,63 +4957,63 @@
       <c r="D32" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="9"/>
       <c r="F32" s="13"/>
       <c r="G32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L32" s="6" t="s">
+      <c r="M32" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
     </row>
-    <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="D33" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E33" s="3"/>
+      <c r="E33" s="9"/>
       <c r="F33" s="13"/>
       <c r="G33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>213</v>
@@ -5054,8 +5026,8 @@
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
     </row>
-    <row r="34" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+    <row r="34" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
         <v>215</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -5073,63 +5045,63 @@
         <v>26</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
     </row>
-    <row r="35" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>221</v>
+    <row r="35" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>222</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="13"/>
       <c r="G35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>225</v>
+        <v>38</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="9"/>
@@ -5137,40 +5109,40 @@
       <c r="Q35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>227</v>
+      <c r="A36" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="13"/>
       <c r="G36" s="1" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="9"/>
@@ -5178,219 +5150,222 @@
       <c r="Q36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
-        <v>228</v>
+      <c r="A37" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="E37" s="3"/>
-      <c r="F37" s="13"/>
+      <c r="F37" s="3"/>
       <c r="G37" s="1" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>207</v>
+        <v>168</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
     </row>
-    <row r="38" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>229</v>
+    <row r="38" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>240</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>179</v>
+        <v>224</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>181</v>
+        <v>38</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
     </row>
-    <row r="39" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>233</v>
+        <v>216</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="13"/>
       <c r="G39" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="M39" s="6" t="s">
-        <v>235</v>
+        <v>62</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>221</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
     </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
-        <v>236</v>
+    <row r="40" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>242</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>238</v>
+        <v>191</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>192</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
+      <c r="G40" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="H40" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>239</v>
+        <v>37</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>240</v>
+        <v>122</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>241</v>
+        <v>62</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="M40" s="8" t="s">
-        <v>243</v>
+        <v>194</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
     </row>
-    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+    <row r="41" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="C41" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="E41" s="3"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H41" s="3" t="s">
+      <c r="M41" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
     </row>
-    <row r="42" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="D42" s="16" t="s">
         <v>252</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -5398,39 +5373,40 @@
         <v>26</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="L42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="M42" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="M42" s="4" t="s">
-        <v>256</v>
-      </c>
       <c r="N42" s="3"/>
+      <c r="O42" s="9"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
     </row>
-    <row r="43" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
+    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="D43" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -5438,40 +5414,39 @@
         <v>26</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>206</v>
+        <v>53</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L43" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="M43" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="M43" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="N43" s="7"/>
-      <c r="O43" s="4"/>
+      <c r="N43" s="3"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
     </row>
-    <row r="44" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+    <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="C44" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="D44" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -5479,40 +5454,40 @@
         <v>26</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="M44" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="M44" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="N44" s="3"/>
-      <c r="O44" s="9"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="4"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
     </row>
-    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="D45" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -5520,368 +5495,368 @@
         <v>26</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="M45" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="M45" s="4" t="s">
-        <v>274</v>
-      </c>
       <c r="N45" s="3"/>
-      <c r="O45" s="4"/>
+      <c r="O45" s="9"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
     </row>
-    <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="13"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
       <c r="G46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L46" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="M46" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="M46" s="4" t="s">
-        <v>280</v>
-      </c>
       <c r="N46" s="3"/>
-      <c r="O46" s="9"/>
+      <c r="O46" s="4"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
     </row>
-    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
+    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>258</v>
-      </c>
       <c r="C47" s="6" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+        <v>283</v>
+      </c>
+      <c r="E47" s="9"/>
+      <c r="F47" s="13"/>
       <c r="G47" s="1" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="M47" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="N47" s="7"/>
-      <c r="O47" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="L47" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="N47" s="3"/>
+      <c r="O47" s="9"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
     </row>
-    <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>282</v>
+    <row r="48" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>286</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="D48" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L48" s="6" t="s">
+      <c r="L48" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="M48" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="M48" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="N48" s="3"/>
-      <c r="O48" s="9"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="4"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
     </row>
     <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>283</v>
+      <c r="A49" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>247</v>
+        <v>270</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="9"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
     </row>
-    <row r="50" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
-        <v>284</v>
+    <row r="50" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="13"/>
+        <v>251</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
       <c r="G50" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>288</v>
+        <v>70</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="9"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
     </row>
-    <row r="51" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+    <row r="51" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="C51" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="D51" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="E51" s="3"/>
+      <c r="E51" s="9"/>
       <c r="F51" s="13"/>
       <c r="G51" s="1" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="M51" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="M51" s="18" t="s">
-        <v>296</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="9"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
     </row>
-    <row r="52" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+    <row r="52" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="D52" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="13"/>
       <c r="G52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="16" t="s">
+      <c r="H52" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="M52" s="18" t="s">
         <v>301</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="M52" s="13" t="s">
-        <v>303</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
     </row>
-    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="D53" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>307</v>
-      </c>
       <c r="E53" s="9"/>
-      <c r="F53" s="13"/>
+      <c r="F53" s="9"/>
       <c r="G53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>294</v>
+      <c r="H53" s="16" t="s">
+        <v>306</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L53" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="M53" s="13" t="s">
         <v>308</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="9"/>
       <c r="P53" s="9"/>
       <c r="Q53" s="9"/>
     </row>
-    <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="D54" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="13"/>
@@ -5889,22 +5864,22 @@
         <v>26</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L54" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="M54" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="M54" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="9"/>
@@ -5913,16 +5888,16 @@
     </row>
     <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="C55" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="D55" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>319</v>
       </c>
       <c r="E55" s="9"/>
       <c r="F55" s="13"/>
@@ -5930,212 +5905,212 @@
         <v>26</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L55" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="M55" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="9"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="9"/>
     </row>
-    <row r="56" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="C56" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="D56" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="E56" s="9"/>
-      <c r="F56" s="3"/>
+      <c r="F56" s="13"/>
       <c r="G56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L56" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M56" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="M56" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="9"/>
     </row>
-    <row r="57" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E57" s="9"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H57" s="16" t="s">
-        <v>301</v>
-      </c>
       <c r="I57" s="1" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="M57" s="13" t="s">
-        <v>303</v>
+        <v>331</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>332</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="9"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="9"/>
     </row>
-    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B58" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H58" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="D58" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="I58" s="1" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L58" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="M58" s="13" t="s">
         <v>308</v>
-      </c>
-      <c r="M58" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
     </row>
-    <row r="59" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="s">
-        <v>330</v>
+    <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>334</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
+        <v>310</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E59" s="9"/>
+      <c r="F59" s="13"/>
       <c r="G59" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L59" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="M59" s="6" t="s">
-        <v>336</v>
+        <v>38</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
     </row>
-    <row r="60" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="D60" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E60" s="3"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>53</v>
@@ -6146,19 +6121,60 @@
       <c r="K60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L60" s="4" t="s">
+      <c r="L60" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="M60" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>342</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
     </row>
+    <row r="61" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="N61" s="3"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:Q60"/>
+  <autoFilter ref="A3:Q61"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
